--- a/Documentation/cdcm_habitatmodel.xlsx
+++ b/Documentation/cdcm_habitatmodel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rashijainx/Library/CloudStorage/Box-Box/Students Rashi Post PhD/IAC 2025/Lunar Habitat Design - Modeling and Evaluating Resilience using CDCM/Work Documentation /"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rashijainx/Documents/GitHub/cdcm_habitatmodel/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2508DE59-7F35-134B-B642-A9BB954C1901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4276BD71-1130-FC40-A994-5DAAD2250F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="3" xr2:uid="{B9866D00-B1EC-D94E-AC1D-0DAFFC8F48F5}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="cdcm_habitat_model " sheetId="3" r:id="rId4"/>
     <sheet name="Time Logs " sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="133">
   <si>
     <t xml:space="preserve">Node </t>
   </si>
@@ -467,14 +467,47 @@
     <t xml:space="preserve">Bringing in important content form "old" folder (on the upper layer) </t>
   </si>
   <si>
-    <t xml:space="preserve">Taking care of written documentation </t>
+    <t xml:space="preserve">Battery </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provides Charge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Function </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Characterstics </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Component </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrical Component </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy Component </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational Context </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added written documentation, Added battery and its documentation from previous work </t>
+  </si>
+  <si>
+    <t>battery.py</t>
+  </si>
+  <si>
+    <t>make_battery</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -551,6 +584,12 @@
       <color theme="9"/>
       <name val="Aptos (Narrow)"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="9"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -572,7 +611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -592,6 +631,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1536,11 +1576,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B0B624-24B4-3947-9671-1232C372D9D7}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1549,23 +1590,60 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
+      <c r="A3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" t="s">
+        <v>122</v>
+      </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1576,8 +1654,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9698938F-4D8A-B84E-B807-6C4A6356B719}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
@@ -1765,6 +1846,9 @@
       <c r="D13" s="10" t="s">
         <v>84</v>
       </c>
+      <c r="E13" s="15" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="D14" s="10" t="s">
@@ -1800,6 +1884,14 @@
       </c>
       <c r="B24" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1828,7 +1920,7 @@
         <v>45880</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/cdcm_habitatmodel.xlsx
+++ b/Documentation/cdcm_habitatmodel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rashijainx/Documents/GitHub/cdcm_habitatmodel/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4276BD71-1130-FC40-A994-5DAAD2250F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5EFDB4-9F00-5540-B526-618DC722E535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="3" xr2:uid="{B9866D00-B1EC-D94E-AC1D-0DAFFC8F48F5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="4" xr2:uid="{B9866D00-B1EC-D94E-AC1D-0DAFFC8F48F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements " sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="141">
   <si>
     <t xml:space="preserve">Node </t>
   </si>
@@ -500,7 +500,31 @@
     <t>battery.py</t>
   </si>
   <si>
-    <t>make_battery</t>
+    <t>make_battery_base</t>
+  </si>
+  <si>
+    <t>make_nonrechargeable_battery</t>
+  </si>
+  <si>
+    <t>make_rechargeable_battery</t>
+  </si>
+  <si>
+    <t>(cbattery in power_models)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(nbattery in power_models) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chargeable and Non-Chargeable Battery Models </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next Steps: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document all power models in the works </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan on next steps for modeling </t>
   </si>
 </sst>
 </file>
@@ -625,13 +649,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1495,10 +1519,10 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="17" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B36" s="13"/>
+      <c r="B36" s="14"/>
       <c r="G36" t="s">
         <v>96</v>
       </c>
@@ -1654,49 +1678,49 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9698938F-4D8A-B84E-B807-6C4A6356B719}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1817,6 +1841,9 @@
       <c r="E9" s="10" t="s">
         <v>68</v>
       </c>
+      <c r="F9" s="13" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="D10" s="10" t="s">
@@ -1825,6 +1852,9 @@
       <c r="E10" s="10" t="s">
         <v>69</v>
       </c>
+      <c r="F10" s="13" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="D11" s="10" t="s">
@@ -1846,7 +1876,7 @@
       <c r="D13" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="13" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1892,6 +1922,22 @@
       </c>
       <c r="B30" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1904,7 +1950,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{602345DC-91ED-E14E-805A-9BB1D795FE31}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1923,6 +1969,27 @@
         <v>130</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="8">
+        <v>45894</v>
+      </c>
+      <c r="B3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Documentation/cdcm_habitatmodel.xlsx
+++ b/Documentation/cdcm_habitatmodel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rashijainx/Documents/GitHub/cdcm_habitatmodel/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5EFDB4-9F00-5540-B526-618DC722E535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4E1572-A017-644A-8354-47E4FDE4F884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="4" xr2:uid="{B9866D00-B1EC-D94E-AC1D-0DAFFC8F48F5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{B9866D00-B1EC-D94E-AC1D-0DAFFC8F48F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements " sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="155">
   <si>
     <t xml:space="preserve">Node </t>
   </si>
@@ -525,6 +525,48 @@
   </si>
   <si>
     <t xml:space="preserve">Plan on next steps for modeling </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allows a Battery to Charge or Discharge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar Arrays </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generates Charge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuclear Reactor </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiring </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carries Charge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage Regulator </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulates Charge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directs Charge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Current Switching Unit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switches Charge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote Powered Controller Module </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Bus Switching Unit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provides Connectivity between Power Channel nad Multiple Downstream Loads </t>
   </si>
 </sst>
 </file>
@@ -1603,13 +1645,13 @@
   <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="70.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>114</v>
       </c>
     </row>
@@ -1648,6 +1690,70 @@
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">

--- a/Documentation/cdcm_habitatmodel.xlsx
+++ b/Documentation/cdcm_habitatmodel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rashijainx/Documents/GitHub/cdcm_habitatmodel/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4E1572-A017-644A-8354-47E4FDE4F884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5716A13-DF48-B444-9927-AA18FCA66239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{B9866D00-B1EC-D94E-AC1D-0DAFFC8F48F5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="156">
   <si>
     <t xml:space="preserve">Node </t>
   </si>
@@ -482,18 +482,6 @@
     <t xml:space="preserve">Characterstics </t>
   </si>
   <si>
-    <t xml:space="preserve">Physical Component </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical Component </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy Component </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operational Context </t>
-  </si>
-  <si>
     <t xml:space="preserve">Added written documentation, Added battery and its documentation from previous work </t>
   </si>
   <si>
@@ -567,6 +555,21 @@
   </si>
   <si>
     <t xml:space="preserve">Provides Connectivity between Power Channel nad Multiple Downstream Loads </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Component, Electrical Component, Energy Component (Provider, Consumer, and Storage), Operational Context </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Component, Energy Provider, Resource Consumer, Operational Context </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Component, Electrical Component, Energy Carrier, Operational Context </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Component, Electrial Component </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Component, Electrical Component, Commandable Component </t>
   </si>
 </sst>
 </file>
@@ -1642,7 +1645,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B0B624-24B4-3947-9671-1232C372D9D7}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.1640625" bestFit="1" customWidth="1"/>
@@ -1674,106 +1677,106 @@
         <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C5" t="s">
-        <v>127</v>
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="C11" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
         <v>150</v>
       </c>
-      <c r="B13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>115</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B21" t="s">
         <v>116</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C21" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C25" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C26" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1948,7 +1951,7 @@
         <v>68</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.25">
@@ -1959,7 +1962,7 @@
         <v>69</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17" x14ac:dyDescent="0.25">
@@ -1983,7 +1986,7 @@
         <v>84</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.25">
@@ -2024,26 +2027,26 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2072,7 +2075,7 @@
         <v>45880</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2080,20 +2083,20 @@
         <v>45894</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
